--- a/result/ITGB1_LUSC_Tables.xlsx
+++ b/result/ITGB1_LUSC_Tables.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +479,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>0.047</t>
         </is>
       </c>
     </row>
@@ -508,342 +510,328 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">  FEMALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>0.699</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FEMALE</t>
+          <t xml:space="preserve">  MALE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>182</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MALE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>179</v>
-      </c>
-      <c r="C8" t="n">
-        <v>182</v>
-      </c>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>110</v>
+      </c>
+      <c r="C9" t="n">
+        <v>128</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.022</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="C10" t="n">
-        <v>128</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.022</t>
-        </is>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
+          <t>pathologic_M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pathologic_M</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>198</v>
+      </c>
+      <c r="C14" t="n">
+        <v>202</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>198</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>202</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.023</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>7</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
+          <t>pathologic_N</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pathologic_N</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>158</v>
+      </c>
+      <c r="C17" t="n">
+        <v>153</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.583</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>158</v>
+        <v>66</v>
       </c>
       <c r="C18" t="n">
-        <v>153</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.583</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
+          <t>pathologic_T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pathologic_T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>51</v>
+      </c>
+      <c r="C22" t="n">
+        <v>58</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.218</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="C23" t="n">
-        <v>58</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.218</t>
-        </is>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="C24" t="n">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>12</v>
-      </c>
-      <c r="C26" t="n">
-        <v>11</v>
-      </c>
+          <t>SmokingStatus</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SmokingStatus</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>40</v>
+      </c>
+      <c r="C27" t="n">
+        <v>36</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.618</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="C28" t="n">
-        <v>36</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.708</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>204</v>
-      </c>
-      <c r="C29" t="n">
         <v>208</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -882,32 +870,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>CDKN2AExpression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>SOX2Expression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>PIK3CAExpression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>NOTCH1Expression</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>age</t>
         </is>
       </c>
     </row>
@@ -929,37 +917,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>0.044</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>-0.080</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.032</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.377</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.103</t>
+          <t>-0.399</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>-0.112</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>-0.105</t>
         </is>
       </c>
     </row>
@@ -967,43 +955,43 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>0.705</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.330</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>0.807</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.038</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.020</t>
         </is>
       </c>
     </row>
@@ -1020,42 +1008,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.019</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.045</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-0.021</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.018</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-0.009</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-0.025</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-0.040</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.040</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
@@ -1063,50 +1051,50 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>0.705</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.802</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.415</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.692</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.420</t>
+          <t>0.981</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1116,12 +1104,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1131,27 +1119,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>-0.045</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-0.116</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.045</t>
+          <t>-0.012</t>
         </is>
       </c>
     </row>
@@ -1159,50 +1147,50 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.330</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.788</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.584</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.785</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDKN2AExpression</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1212,17 +1200,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>-0.045</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1232,22 +1220,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.033</t>
+          <t>0.058</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.068</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>0.196</t>
         </is>
       </c>
     </row>
@@ -1255,50 +1243,50 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.802</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.501</t>
+          <t>0.200</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOX2Expression</t>
+          <t>CDKN2AExpression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1308,22 +1296,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.377</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.021</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1333,17 +1321,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.147</t>
+          <t>-0.074</t>
         </is>
       </c>
     </row>
@@ -1351,50 +1339,50 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.807</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.788</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.104</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PIK3CAExpression</t>
+          <t>SOX2Expression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1404,27 +1392,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.103</t>
+          <t>-0.399</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-0.116</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.033</t>
+          <t>0.058</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1434,12 +1422,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.036</t>
+          <t>0.528</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>0.004</t>
         </is>
       </c>
     </row>
@@ -1447,50 +1435,50 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.501</t>
+          <t>0.200</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.527</t>
+          <t>0.933</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NOTCH1Expression</t>
+          <t>PIK3CAExpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1500,32 +1488,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>-0.112</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.068</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.036</t>
+          <t>0.528</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1535,7 +1523,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.032</t>
         </is>
       </c>
     </row>
@@ -1543,50 +1531,50 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.584</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.987</t>
+          <t>0.482</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>NOTCH1Expression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1596,37 +1584,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>-0.105</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.040</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.045</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.147</t>
+          <t>-0.074</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.032</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1639,42 +1627,42 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.420</t>
+          <t>0.981</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.785</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.527</t>
+          <t>0.933</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.987</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1690,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1706,6 +1694,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>P-value</t>
         </is>
       </c>
@@ -1719,7 +1717,13 @@
       <c r="B2" t="n">
         <v>1.021</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>0.031</t>
         </is>
@@ -1734,7 +1738,13 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.986</t>
         </is>
@@ -1749,7 +1759,13 @@
       <c r="B4" t="n">
         <v>0.8070000000000001</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.163</t>
         </is>
@@ -1764,7 +1780,13 @@
       <c r="B5" t="n">
         <v>1.241</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>0.226</t>
         </is>
@@ -1779,7 +1801,13 @@
       <c r="B6" t="n">
         <v>0.997</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>0.987</t>
         </is>
@@ -1794,7 +1822,13 @@
       <c r="B7" t="n">
         <v>1.366</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.031</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>0.123</t>
         </is>
@@ -1809,7 +1843,13 @@
       <c r="B8" t="n">
         <v>2.791</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.085</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.031</t>
         </is>
@@ -1826,12 +1866,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Clinical Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Hazard Ratio (HR)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.920</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.432</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ITGB1group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.767</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.207</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Variable</t>
         </is>
       </c>
@@ -1842,15 +2028,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1858,13 +2039,12 @@
     </row>
     <row r="2">
       <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
         <v/>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1879,7 +2059,6 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1889,12 +2068,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ITGB1expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
+          <t>ITGB1expression ~ age + number_pack_years_smoked + C(gender)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1904,12 +2082,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0242</t>
+          <t>0.0056</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1919,12 +2096,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.2913e-01</t>
+          <t>5.1350e-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1935,7 +2111,6 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1944,17 +2119,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7270.4003</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2208.8191</v>
-      </c>
-      <c r="D8" t="n">
-        <v>12331.9816</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.005</t>
+        <v>7841.803</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2893.421-12790.185</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.002</t>
         </is>
       </c>
     </row>
@@ -1965,794 +2139,1003 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>303.6114</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1039.3226</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1646.5453</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.657</t>
+        <v>434.291</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-906.538-1775.119</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.525</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1329.2122</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.4001</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2659.8244</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.050</t>
+        <v>48.139</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-22.663-118.941</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.182</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>772.7641</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-898.2487</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2443.777</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.364</t>
+        <v>2.26</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-16.618-21.137</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.814</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5456.8922</v>
-      </c>
-      <c r="C12" t="n">
-        <v>537.4707</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10376.3137</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.030</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>48.5322</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-22.755</v>
-      </c>
-      <c r="D13" t="n">
-        <v>119.8194</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.182</t>
-        </is>
-      </c>
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.7391</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-16.1256</v>
-      </c>
-      <c r="D14" t="n">
-        <v>21.6037</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.775</t>
-        </is>
-      </c>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ITGB1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0242</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ITGB1expression</t>
+          <t>1.2913e-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ITGB1expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0160</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7270.4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2208.819-12331.982</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3.6460e-01</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>303.611</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-1039.323-1646.545</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.657</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1329.212</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-1.4-2659.824</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.050</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_stage)[T.3.0]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6872.6268</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1837.4119</v>
-      </c>
-      <c r="D22" t="n">
-        <v>11907.8416</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.008</t>
+        <v>772.764</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-898.249-2443.777</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.364</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_stage)[T.4.0]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>347.825</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-1008.3951</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1704.0451</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.614</t>
+        <v>5456.892</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>537.471-10376.314</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.030</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.2.0]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>956.1882000000001</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-496.4963</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2408.8727</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.196</t>
+        <v>48.532</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-22.755-119.819</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.182</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.3.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2120.0573</v>
-      </c>
-      <c r="C25" t="n">
-        <v>79.92359999999999</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4160.191</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.042</t>
+        <v>2.739</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-16.126-21.604</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.775</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>971.0846</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-2169.7124</v>
-      </c>
-      <c r="D26" t="n">
-        <v>4111.8816</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.544</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>49.6126</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-21.3161</v>
-      </c>
-      <c r="D27" t="n">
-        <v>120.5413</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.170</t>
-        </is>
-      </c>
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3.1182</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-15.7701</v>
-      </c>
-      <c r="D28" t="n">
-        <v>22.0066</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.746</t>
-        </is>
-      </c>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ITGB1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0160</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ITGB1expression</t>
+          <t>3.6460e-01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ITGB1expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0.0128</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>6872.627</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1837.412-11907.842</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>5.2260e-01</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>347.825</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-1008.395-1704.045</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.614</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>956.188</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-496.496-2408.873</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_T)[T.3.0]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7582.3807</v>
-      </c>
-      <c r="C36" t="n">
-        <v>2439.4563</v>
-      </c>
-      <c r="D36" t="n">
-        <v>12725.305</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.004</t>
+        <v>2120.057</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>79.924-4160.191</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.042</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_T)[T.4.0]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>431.1941</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-918.8176999999999</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1781.2059</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.530</t>
+        <v>971.085</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-2169.712-4111.882</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.544</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.1.0]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>738.9382000000001</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-632.4915999999999</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2110.3679</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.290</t>
+        <v>49.613</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-21.316-120.541</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.170</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.2.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1145.7383</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-3363.8983</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1072.4216</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.311</t>
+        <v>3.118</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-15.77-22.007</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.746</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>43.9815</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-5969.9522</v>
-      </c>
-      <c r="D40" t="n">
-        <v>6057.9153</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.989</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>50.2561</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-22.5173</v>
-      </c>
-      <c r="D41" t="n">
-        <v>123.0296</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.175</t>
-        </is>
-      </c>
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2.6926</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-16.3398</v>
-      </c>
-      <c r="D42" t="n">
-        <v>21.725</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.781</t>
-        </is>
-      </c>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ITGB1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0128</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ITGB1expression</t>
+          <t>5.2260e-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ITGB1expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0172</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>7582.381</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2439.456-12725.305</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2.0376e-01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>431.194</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-918.818-1781.206</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.530</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>738.938</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-632.492-2110.368</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.290</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_N)[T.2.0]</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7596.1394</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1792.8225</v>
-      </c>
-      <c r="D50" t="n">
-        <v>13399.4562</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0.010</t>
+        <v>-1145.738</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-3363.898-1072.422</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.311</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_N)[T.3.0]</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>757.0653</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-783.5663</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2297.697</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.334</t>
+        <v>43.982</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-5969.952-6057.915</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.989</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C(pathologic_M)[T.1.0]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4627.582</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-486.6125</v>
-      </c>
-      <c r="D52" t="n">
-        <v>9741.776400000001</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.076</t>
+        <v>50.256</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-22.517-123.03</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.175</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>49.057</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-33.4087</v>
-      </c>
-      <c r="D53" t="n">
-        <v>131.5227</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.243</t>
+        <v>2.693</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-16.34-21.725</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0.781</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>3.0511</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-18.6294</v>
-      </c>
-      <c r="D54" t="n">
-        <v>24.7315</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.782</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ITGB1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0172</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2.0376e-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>7596.139</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1792.822-13399.456</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>757.0650000000001</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-783.566-2297.697</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4627.582</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-486.612-9741.776</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0.076</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>49.057</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-33.409-131.523</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0.243</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3.051</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-18.629-24.732</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0.782</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cancer Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chi-square</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ITGB1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5.123</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ITGB1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6.366</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
